--- a/Result/profitability/1219.xlsx
+++ b/Result/profitability/1219.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.38</v>
       </c>
       <c r="M2" t="n">
-        <v>0.14375</v>
+        <v>0.01249999999999997</v>
       </c>
       <c r="N2" t="n">
-        <v>8.991250000000001</v>
+        <v>8.216249999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>0.05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.145</v>
+        <v>-0.002500000000000032</v>
       </c>
       <c r="N3" t="n">
-        <v>8.68125</v>
+        <v>7.7275</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>0.12125</v>
+        <v>-0.01750000000000003</v>
       </c>
       <c r="N4" t="n">
-        <v>8.23</v>
+        <v>7.476249999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.54</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04124999999999997</v>
+        <v>-0.08000000000000004</v>
       </c>
       <c r="N5" t="n">
-        <v>6.79</v>
+        <v>6.32875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.21</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07249999999999997</v>
+        <v>-0.07750000000000004</v>
       </c>
       <c r="N6" t="n">
-        <v>6.9875</v>
+        <v>6.14625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.36</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09374999999999997</v>
+        <v>-0.05750000000000005</v>
       </c>
       <c r="N7" t="n">
-        <v>7.22625</v>
+        <v>6.35</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.14</v>
       </c>
       <c r="M8" t="n">
-        <v>0.08624999999999997</v>
+        <v>-0.05375000000000005</v>
       </c>
       <c r="N8" t="n">
-        <v>6.97875</v>
+        <v>6.3325</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.2</v>
       </c>
       <c r="M9" t="n">
-        <v>0.09749999999999998</v>
+        <v>0.09749999999999995</v>
       </c>
       <c r="N9" t="n">
         <v>6.96875</v>
@@ -1645,7 +1645,7 @@
         <v>0.11</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06374999999999997</v>
+        <v>0.06374999999999996</v>
       </c>
       <c r="N10" t="n">
         <v>6.59</v>
@@ -1772,7 +1772,7 @@
         <v>0.14</v>
       </c>
       <c r="M11" t="n">
-        <v>0.07499999999999997</v>
+        <v>0.07499999999999996</v>
       </c>
       <c r="N11" t="n">
         <v>6.79125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3335</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3247</v>
+      </c>
+      <c r="E75" t="n">
+        <v>88</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-204</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-6.11%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-213</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-417</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-345</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.03000000000000003</v>
+      </c>
+      <c r="N75" t="n">
+        <v>7.9475</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-10.18181818181818</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.17</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.6619718309859155</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.69</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.5829383886255923</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
